--- a/results/greedy/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02286970795830712</v>
+        <v>0.02312658401206136</v>
       </c>
       <c r="C2" t="n">
         <v>20.63867171659499</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02801975002512336</v>
+        <v>0.02687579102348536</v>
       </c>
       <c r="C2" t="n">
         <v>14.88853964341589</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02044195798225701</v>
+        <v>0.02058833400951698</v>
       </c>
       <c r="C2" t="n">
         <v>18.63602924938197</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02764275000663474</v>
+        <v>0.02711787499720231</v>
       </c>
       <c r="C2" t="n">
         <v>21.72486829171405</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02776158298365772</v>
+        <v>0.0281692499993369</v>
       </c>
       <c r="C2" t="n">
         <v>18.95974535972078</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02621824998641387</v>
+        <v>0.02603091701166704</v>
       </c>
       <c r="C2" t="n">
         <v>19.94236788887022</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276716602500528</v>
+        <v>0.02247491700109094</v>
       </c>
       <c r="C2" t="n">
         <v>21.57538026951271</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02088033297332004</v>
+        <v>0.02017541701206937</v>
       </c>
       <c r="C2" t="n">
         <v>18.46452580087577</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02321491698967293</v>
+        <v>0.02267987502273172</v>
       </c>
       <c r="C2" t="n">
         <v>21.05385701732143</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02272841596277431</v>
+        <v>0.02311916596954688</v>
       </c>
       <c r="C2" t="n">
         <v>23.19287124622353</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02061204198980704</v>
+        <v>0.02023733296664432</v>
       </c>
       <c r="C2" t="n">
         <v>15.12099573136445</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02424191602040082</v>
+        <v>0.02386141597526148</v>
       </c>
       <c r="C2" t="n">
         <v>15.43586028420507</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0256293750135228</v>
+        <v>0.02667429199209437</v>
       </c>
       <c r="C2" t="n">
         <v>21.21282024109146</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337608399102464</v>
+        <v>0.02336066699353978</v>
       </c>
       <c r="C2" t="n">
         <v>15.27084253729069</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0311378330225125</v>
+        <v>0.0324591250391677</v>
       </c>
       <c r="C2" t="n">
         <v>17.53239021051001</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02403916703769937</v>
+        <v>0.02420179196633399</v>
       </c>
       <c r="C2" t="n">
         <v>19.8593791658789</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02731741702882573</v>
+        <v>0.02740908297710121</v>
       </c>
       <c r="C2" t="n">
         <v>20.47739820495473</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01907350000692531</v>
+        <v>0.01938245899509639</v>
       </c>
       <c r="C2" t="n">
         <v>18.06377249243819</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01859437499660999</v>
+        <v>0.01946454198332503</v>
       </c>
       <c r="C2" t="n">
         <v>21.38076136576417</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02810108300764114</v>
+        <v>0.0282521250192076</v>
       </c>
       <c r="C2" t="n">
         <v>24.51961475534245</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02173608302837238</v>
+        <v>0.02161941601661965</v>
       </c>
       <c r="C2" t="n">
         <v>21.43546298444437</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02855883300071582</v>
+        <v>0.02813670795876533</v>
       </c>
       <c r="C2" t="n">
         <v>17.99718357398262</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236641600029543</v>
+        <v>0.02223591698566452</v>
       </c>
       <c r="C2" t="n">
         <v>17.64728642791695</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02293412503786385</v>
+        <v>0.02303629199741408</v>
       </c>
       <c r="C2" t="n">
         <v>21.00502656786053</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01976812502834946</v>
+        <v>0.02024049998726696</v>
       </c>
       <c r="C2" t="n">
         <v>18.65355665934624</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03035479201935232</v>
+        <v>0.03120904101524502</v>
       </c>
       <c r="C2" t="n">
         <v>24.03097877472007</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0204114579828456</v>
+        <v>0.02103908295975998</v>
       </c>
       <c r="C2" t="n">
         <v>24.74102448296927</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02515220904024318</v>
+        <v>0.02493258396862075</v>
       </c>
       <c r="C2" t="n">
         <v>15.24133228650409</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450070797931403</v>
+        <v>0.02483541698893532</v>
       </c>
       <c r="C2" t="n">
         <v>16.07073642638597</v>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0255254169460386</v>
+        <v>0.02523962501436472</v>
       </c>
       <c r="C2" t="n">
         <v>21.06001479006229</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02770845801569521</v>
+        <v>0.02707400004146621</v>
       </c>
       <c r="C2" t="n">
         <v>18.87992759026107</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02750625001499429</v>
+        <v>0.02797137497691438</v>
       </c>
       <c r="C2" t="n">
         <v>21.42469980251549</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02915633301017806</v>
+        <v>0.02918237500125542</v>
       </c>
       <c r="C2" t="n">
         <v>17.82455587296945</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02589404099853709</v>
+        <v>0.02553700003772974</v>
       </c>
       <c r="C2" t="n">
         <v>21.49209116317056</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02167320903390646</v>
+        <v>0.02148837497225031</v>
       </c>
       <c r="C2" t="n">
         <v>17.70912531190438</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01582629099721089</v>
+        <v>0.01547354203648865</v>
       </c>
       <c r="C2" t="n">
         <v>16.62902317961131</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02283291600178927</v>
+        <v>0.02207120804814622</v>
       </c>
       <c r="C2" t="n">
         <v>21.36311016663718</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02753420895896852</v>
+        <v>0.02673079195665196</v>
       </c>
       <c r="C2" t="n">
         <v>20.73320581923262</v>
@@ -4605,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02724124997621402</v>
+        <v>0.02701395796611905</v>
       </c>
       <c r="C2" t="n">
         <v>18.65241279899197</v>
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388029097346589</v>
+        <v>0.02469191700220108</v>
       </c>
       <c r="C2" t="n">
         <v>19.07248324744826</v>
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02213649998884648</v>
+        <v>0.02218187501421198</v>
       </c>
       <c r="C2" t="n">
         <v>19.52205978050317</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02237279195105657</v>
+        <v>0.02183879096992314</v>
       </c>
       <c r="C2" t="n">
         <v>22.77269224399739</v>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01910520798992366</v>
+        <v>0.01909750001505017</v>
       </c>
       <c r="C2" t="n">
         <v>19.48688997860929</v>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02402349998010322</v>
+        <v>0.02376495895441622</v>
       </c>
       <c r="C2" t="n">
         <v>19.17133011578246</v>
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648991701425985</v>
+        <v>0.02640320803038776</v>
       </c>
       <c r="C2" t="n">
         <v>17.75043366651897</v>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02135929197538644</v>
+        <v>0.02263783401576802</v>
       </c>
       <c r="C2" t="n">
         <v>27.47120112194591</v>
@@ -5453,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02345141698606312</v>
+        <v>0.02436512499116361</v>
       </c>
       <c r="C2" t="n">
         <v>19.58478573018044</v>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02076616702834144</v>
+        <v>0.02098179201129824</v>
       </c>
       <c r="C2" t="n">
         <v>18.97302986402446</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02195312501862645</v>
+        <v>0.021870750002563</v>
       </c>
       <c r="C2" t="n">
         <v>19.970235586311</v>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02120004198513925</v>
+        <v>0.02068704197881743</v>
       </c>
       <c r="C2" t="n">
         <v>22.0247907450957</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02117874997202307</v>
+        <v>0.02060716698179021</v>
       </c>
       <c r="C2" t="n">
         <v>16.70758114886709</v>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02778370800660923</v>
+        <v>0.02717295900220051</v>
       </c>
       <c r="C2" t="n">
         <v>24.92880422837947</v>
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0270429159863852</v>
+        <v>0.02650020900182426</v>
       </c>
       <c r="C2" t="n">
         <v>25.10808579590247</v>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630920801311731</v>
+        <v>0.0286722500459291</v>
       </c>
       <c r="C2" t="n">
         <v>17.97646739791893</v>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02006929204799235</v>
+        <v>0.0209785420447588</v>
       </c>
       <c r="C2" t="n">
         <v>16.93855313043346</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01962408301187679</v>
+        <v>0.019860458036419</v>
       </c>
       <c r="C2" t="n">
         <v>16.53384112354741</v>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03322237503016368</v>
+        <v>0.03305412497138605</v>
       </c>
       <c r="C2" t="n">
         <v>14.54048625680572</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01951225002994761</v>
+        <v>0.02753050002502277</v>
       </c>
       <c r="C2" t="n">
         <v>20.769742585002</v>
@@ -6725,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02326437504962087</v>
+        <v>0.02349500003037974</v>
       </c>
       <c r="C2" t="n">
         <v>19.52813750438344</v>
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401404199190438</v>
+        <v>0.0252636669902131</v>
       </c>
       <c r="C2" t="n">
         <v>21.40450980265863</v>
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03197816701140255</v>
+        <v>0.03377487498801202</v>
       </c>
       <c r="C2" t="n">
         <v>27.9568306652521</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02380054199602455</v>
+        <v>0.02466404199367389</v>
       </c>
       <c r="C2" t="n">
         <v>18.06764908389514</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02222329203505069</v>
+        <v>0.02215175004675984</v>
       </c>
       <c r="C2" t="n">
         <v>18.84428488262762</v>
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01540899998508394</v>
+        <v>0.01516220800112933</v>
       </c>
       <c r="C2" t="n">
         <v>20.33434891660794</v>
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0229606669745408</v>
+        <v>0.02393808303168043</v>
       </c>
       <c r="C2" t="n">
         <v>19.52600944794802</v>
@@ -7467,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01889670803211629</v>
+        <v>0.01988237496698275</v>
       </c>
       <c r="C2" t="n">
         <v>20.20679182256417</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01805466698715463</v>
+        <v>0.01814537501195446</v>
       </c>
       <c r="C2" t="n">
         <v>17.82411587578753</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02362833300139755</v>
+        <v>0.02450987498741597</v>
       </c>
       <c r="C2" t="n">
         <v>19.81379386545238</v>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02000358299119398</v>
+        <v>0.02278041699901223</v>
       </c>
       <c r="C2" t="n">
         <v>14.5813319818636</v>
@@ -7891,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02437524998094887</v>
+        <v>0.02441070805070922</v>
       </c>
       <c r="C2" t="n">
         <v>17.32833414225857</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02170066704275087</v>
+        <v>0.02146495803026482</v>
       </c>
       <c r="C2" t="n">
         <v>17.78098001925608</v>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02969329198822379</v>
+        <v>0.02898483298486099</v>
       </c>
       <c r="C2" t="n">
         <v>21.02331963911671</v>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02111687499564141</v>
+        <v>0.02078558300854638</v>
       </c>
       <c r="C2" t="n">
         <v>18.89873868520927</v>
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02015812497120351</v>
+        <v>0.02014824998332188</v>
       </c>
       <c r="C2" t="n">
         <v>18.86244694022617</v>
@@ -8421,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922704198863357</v>
+        <v>0.02864604198839515</v>
       </c>
       <c r="C2" t="n">
         <v>23.89280090759444</v>
@@ -8527,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118987496942282</v>
+        <v>0.02085004199761897</v>
       </c>
       <c r="C2" t="n">
         <v>18.75921034956803</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01843870803713799</v>
+        <v>0.01825800002552569</v>
       </c>
       <c r="C2" t="n">
         <v>16.05572095033472</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337324997643009</v>
+        <v>0.0230089999968186</v>
       </c>
       <c r="C2" t="n">
         <v>20.1798782393949</v>
@@ -8845,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02205274999141693</v>
+        <v>0.02159104199381545</v>
       </c>
       <c r="C2" t="n">
         <v>16.18201552721885</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01922237500548363</v>
+        <v>0.01885304198367521</v>
       </c>
       <c r="C2" t="n">
         <v>21.95026985142217</v>
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01823654200416058</v>
+        <v>0.01796366600319743</v>
       </c>
       <c r="C2" t="n">
         <v>22.57096926733922</v>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0267292499775067</v>
+        <v>0.02655908395536244</v>
       </c>
       <c r="C2" t="n">
         <v>26.24079228157473</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01888962497469038</v>
+        <v>0.01860999997006729</v>
       </c>
       <c r="C2" t="n">
         <v>13.9518462508164</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02955616603139788</v>
+        <v>0.0299744579824619</v>
       </c>
       <c r="C2" t="n">
         <v>17.56174429888955</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450300002237782</v>
+        <v>0.02433020796161145</v>
       </c>
       <c r="C2" t="n">
         <v>15.0082036870514</v>
@@ -9587,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02038200001697987</v>
+        <v>0.02008324995404109</v>
       </c>
       <c r="C2" t="n">
         <v>13.53026701633701</v>
@@ -9693,7 +9693,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02352541696745902</v>
+        <v>0.02307350002229214</v>
       </c>
       <c r="C2" t="n">
         <v>18.29294551819477</v>
@@ -9799,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02164454199373722</v>
+        <v>0.02132450003409758</v>
       </c>
       <c r="C2" t="n">
         <v>23.04578310431127</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02374291600426659</v>
+        <v>0.02537799999117851</v>
       </c>
       <c r="C2" t="n">
         <v>20.73613737729362</v>
@@ -10011,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01920720800990239</v>
+        <v>0.01896549999946728</v>
       </c>
       <c r="C2" t="n">
         <v>15.71535626489778</v>
@@ -10117,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932241698727012</v>
+        <v>0.03047162498114631</v>
       </c>
       <c r="C2" t="n">
         <v>13.58452293746157</v>
@@ -10223,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0234328749938868</v>
+        <v>0.02345650002826005</v>
       </c>
       <c r="C2" t="n">
         <v>22.02191240296806</v>
@@ -10329,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01929108297917992</v>
+        <v>0.01961287501035258</v>
       </c>
       <c r="C2" t="n">
         <v>18.36045661822892</v>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02459762501530349</v>
+        <v>0.02511395799228922</v>
       </c>
       <c r="C2" t="n">
         <v>14.45958866132876</v>
@@ -10541,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02484483399894089</v>
+        <v>0.02673641702858731</v>
       </c>
       <c r="C2" t="n">
         <v>20.89059430978426</v>
@@ -10647,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02343474997906014</v>
+        <v>0.0233332909992896</v>
       </c>
       <c r="C2" t="n">
         <v>18.95235926736388</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02159870899049565</v>
+        <v>0.02179629198508337</v>
       </c>
       <c r="C2" t="n">
         <v>12.10075358302809</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01773062499705702</v>
+        <v>0.01770954194944352</v>
       </c>
       <c r="C2" t="n">
         <v>25.30118968960324</v>
@@ -10965,7 +10965,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392329199938104</v>
+        <v>0.02479883300838992</v>
       </c>
       <c r="C2" t="n">
         <v>18.66458328026794</v>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02176691597560421</v>
+        <v>0.02255512500414625</v>
       </c>
       <c r="C2" t="n">
         <v>21.65649280520064</v>

--- a/results/greedy/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02312658401206136</v>
+        <v>0.02226091700140387</v>
       </c>
       <c r="C2" t="n">
         <v>20.63867171659499</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02687579102348536</v>
+        <v>0.02674612501868978</v>
       </c>
       <c r="C2" t="n">
         <v>14.88853964341589</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02058833400951698</v>
+        <v>0.01970799994887784</v>
       </c>
       <c r="C2" t="n">
         <v>18.63602924938197</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02711787499720231</v>
+        <v>0.02676433400483802</v>
       </c>
       <c r="C2" t="n">
         <v>21.72486829171405</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0281692499993369</v>
+        <v>0.02743324998300523</v>
       </c>
       <c r="C2" t="n">
         <v>18.95974535972078</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02603091701166704</v>
+        <v>0.02622345898998901</v>
       </c>
       <c r="C2" t="n">
         <v>19.94236788887022</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02247491700109094</v>
+        <v>0.02198870800202712</v>
       </c>
       <c r="C2" t="n">
         <v>21.57538026951271</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02017541701206937</v>
+        <v>0.02009458298562095</v>
       </c>
       <c r="C2" t="n">
         <v>18.46452580087577</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02267987502273172</v>
+        <v>0.02282133395783603</v>
       </c>
       <c r="C2" t="n">
         <v>21.05385701732143</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02311916596954688</v>
+        <v>0.02225062501383945</v>
       </c>
       <c r="C2" t="n">
         <v>23.19287124622353</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023733296664432</v>
+        <v>0.02020608296152204</v>
       </c>
       <c r="C2" t="n">
         <v>15.12099573136445</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02386141597526148</v>
+        <v>0.02390870900126174</v>
       </c>
       <c r="C2" t="n">
         <v>15.43586028420507</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02667429199209437</v>
+        <v>0.02522233297349885</v>
       </c>
       <c r="C2" t="n">
         <v>21.21282024109146</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02336066699353978</v>
+        <v>0.02246350003406405</v>
       </c>
       <c r="C2" t="n">
         <v>15.27084253729069</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0324591250391677</v>
+        <v>0.03037154203047976</v>
       </c>
       <c r="C2" t="n">
         <v>17.53239021051001</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02420179196633399</v>
+        <v>0.0236456660204567</v>
       </c>
       <c r="C2" t="n">
         <v>19.8593791658789</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02740908297710121</v>
+        <v>0.02721179195214063</v>
       </c>
       <c r="C2" t="n">
         <v>20.47739820495473</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01938245899509639</v>
+        <v>0.01848487497773021</v>
       </c>
       <c r="C2" t="n">
         <v>18.06377249243819</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01946454198332503</v>
+        <v>0.01824495801702142</v>
       </c>
       <c r="C2" t="n">
         <v>21.38076136576417</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0282521250192076</v>
+        <v>0.02748070802772418</v>
       </c>
       <c r="C2" t="n">
         <v>24.51961475534245</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02161941601661965</v>
+        <v>0.02126737503567711</v>
       </c>
       <c r="C2" t="n">
         <v>21.43546298444437</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02813670795876533</v>
+        <v>0.02782874996773899</v>
       </c>
       <c r="C2" t="n">
         <v>17.99718357398262</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02223591698566452</v>
+        <v>0.02171699999598786</v>
       </c>
       <c r="C2" t="n">
         <v>17.64728642791695</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303629199741408</v>
+        <v>0.02288716699695215</v>
       </c>
       <c r="C2" t="n">
         <v>21.00502656786053</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02024049998726696</v>
+        <v>0.01934687496395782</v>
       </c>
       <c r="C2" t="n">
         <v>18.65355665934624</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03120904101524502</v>
+        <v>0.02975016599521041</v>
       </c>
       <c r="C2" t="n">
         <v>24.03097877472007</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02103908295975998</v>
+        <v>0.02016287500737235</v>
       </c>
       <c r="C2" t="n">
         <v>24.74102448296927</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02493258396862075</v>
+        <v>0.02454704098636284</v>
       </c>
       <c r="C2" t="n">
         <v>15.24133228650409</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02483541698893532</v>
+        <v>0.02412254200316966</v>
       </c>
       <c r="C2" t="n">
         <v>16.07073642638597</v>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523962501436472</v>
+        <v>0.02527308400021866</v>
       </c>
       <c r="C2" t="n">
         <v>21.06001479006229</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02707400004146621</v>
+        <v>0.02687391696963459</v>
       </c>
       <c r="C2" t="n">
         <v>18.87992759026107</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02797137497691438</v>
+        <v>0.02724612504243851</v>
       </c>
       <c r="C2" t="n">
         <v>21.42469980251549</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02918237500125542</v>
+        <v>0.02853541699005291</v>
       </c>
       <c r="C2" t="n">
         <v>17.82455587296945</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02553700003772974</v>
+        <v>0.02560770901618525</v>
       </c>
       <c r="C2" t="n">
         <v>21.49209116317056</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02148837497225031</v>
+        <v>0.0212336250115186</v>
       </c>
       <c r="C2" t="n">
         <v>17.70912531190438</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01547354203648865</v>
+        <v>0.01529212499735877</v>
       </c>
       <c r="C2" t="n">
         <v>16.62902317961131</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02207120804814622</v>
+        <v>0.02209541702177376</v>
       </c>
       <c r="C2" t="n">
         <v>21.36311016663718</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02673079195665196</v>
+        <v>0.02702391700586304</v>
       </c>
       <c r="C2" t="n">
         <v>20.73320581923262</v>
@@ -4605,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02701395796611905</v>
+        <v>0.0268837499897927</v>
       </c>
       <c r="C2" t="n">
         <v>18.65241279899197</v>
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02469191700220108</v>
+        <v>0.02345683297608048</v>
       </c>
       <c r="C2" t="n">
         <v>19.07248324744826</v>
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02218187501421198</v>
+        <v>0.02183749998221174</v>
       </c>
       <c r="C2" t="n">
         <v>19.52205978050317</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02183879096992314</v>
+        <v>0.02187866601161659</v>
       </c>
       <c r="C2" t="n">
         <v>22.77269224399739</v>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01909750001505017</v>
+        <v>0.01862895803060383</v>
       </c>
       <c r="C2" t="n">
         <v>19.48688997860929</v>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02376495895441622</v>
+        <v>0.02342987502925098</v>
       </c>
       <c r="C2" t="n">
         <v>19.17133011578246</v>
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02640320803038776</v>
+        <v>0.02611108403652906</v>
       </c>
       <c r="C2" t="n">
         <v>17.75043366651897</v>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02263783401576802</v>
+        <v>0.02070641698082909</v>
       </c>
       <c r="C2" t="n">
         <v>27.47120112194591</v>
@@ -5453,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02436512499116361</v>
+        <v>0.02306012500775978</v>
       </c>
       <c r="C2" t="n">
         <v>19.58478573018044</v>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02098179201129824</v>
+        <v>0.02014962496468797</v>
       </c>
       <c r="C2" t="n">
         <v>18.97302986402446</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.021870750002563</v>
+        <v>0.02149066596757621</v>
       </c>
       <c r="C2" t="n">
         <v>19.970235586311</v>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02068704197881743</v>
+        <v>0.02054033300373703</v>
       </c>
       <c r="C2" t="n">
         <v>22.0247907450957</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02060716698179021</v>
+        <v>0.02050033397972584</v>
       </c>
       <c r="C2" t="n">
         <v>16.70758114886709</v>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717295900220051</v>
+        <v>0.02696504100458696</v>
       </c>
       <c r="C2" t="n">
         <v>24.92880422837947</v>
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650020900182426</v>
+        <v>0.0265468749566935</v>
       </c>
       <c r="C2" t="n">
         <v>25.10808579590247</v>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0286722500459291</v>
+        <v>0.02610066696070135</v>
       </c>
       <c r="C2" t="n">
         <v>17.97646739791893</v>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0209785420447588</v>
+        <v>0.01954887504689395</v>
       </c>
       <c r="C2" t="n">
         <v>16.93855313043346</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.019860458036419</v>
+        <v>0.0192672090488486</v>
       </c>
       <c r="C2" t="n">
         <v>16.53384112354741</v>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03305412497138605</v>
+        <v>0.03299312497256324</v>
       </c>
       <c r="C2" t="n">
         <v>14.54048625680572</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02753050002502277</v>
+        <v>0.01910470897564664</v>
       </c>
       <c r="C2" t="n">
         <v>20.769742585002</v>
@@ -6725,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02349500003037974</v>
+        <v>0.02294741704827175</v>
       </c>
       <c r="C2" t="n">
         <v>19.52813750438344</v>
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252636669902131</v>
+        <v>0.02387708402238786</v>
       </c>
       <c r="C2" t="n">
         <v>21.40450980265863</v>
@@ -6937,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03377487498801202</v>
+        <v>0.03150687500601634</v>
       </c>
       <c r="C2" t="n">
         <v>27.9568306652521</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02466404199367389</v>
+        <v>0.02335908298846334</v>
       </c>
       <c r="C2" t="n">
         <v>18.06764908389514</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02215175004675984</v>
+        <v>0.02196158398874104</v>
       </c>
       <c r="C2" t="n">
         <v>18.84428488262762</v>
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01516220800112933</v>
+        <v>0.01522699999623001</v>
       </c>
       <c r="C2" t="n">
         <v>20.33434891660794</v>
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02393808303168043</v>
+        <v>0.0225861250073649</v>
       </c>
       <c r="C2" t="n">
         <v>19.52600944794802</v>
@@ -7467,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01988237496698275</v>
+        <v>0.01836429198738188</v>
       </c>
       <c r="C2" t="n">
         <v>20.20679182256417</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01814537501195446</v>
+        <v>0.01776799996150658</v>
       </c>
       <c r="C2" t="n">
         <v>17.82411587578753</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450987498741597</v>
+        <v>0.02331945800688118</v>
       </c>
       <c r="C2" t="n">
         <v>19.81379386545238</v>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02278041699901223</v>
+        <v>0.019475249981042</v>
       </c>
       <c r="C2" t="n">
         <v>14.5813319818636</v>
@@ -7891,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02441070805070922</v>
+        <v>0.02404841699171811</v>
       </c>
       <c r="C2" t="n">
         <v>17.32833414225857</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02146495803026482</v>
+        <v>0.02131124999141321</v>
       </c>
       <c r="C2" t="n">
         <v>17.78098001925608</v>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02898483298486099</v>
+        <v>0.02906241704476997</v>
       </c>
       <c r="C2" t="n">
         <v>21.02331963911671</v>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02078558300854638</v>
+        <v>0.02059924998320639</v>
       </c>
       <c r="C2" t="n">
         <v>18.89873868520927</v>
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02014824998332188</v>
+        <v>0.01946012501139194</v>
       </c>
       <c r="C2" t="n">
         <v>18.86244694022617</v>
@@ -8421,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02864604198839515</v>
+        <v>0.02871862496249378</v>
       </c>
       <c r="C2" t="n">
         <v>23.89280090759444</v>
@@ -8527,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02085004199761897</v>
+        <v>0.02076662500621751</v>
       </c>
       <c r="C2" t="n">
         <v>18.75921034956803</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01825800002552569</v>
+        <v>0.01821158296661451</v>
       </c>
       <c r="C2" t="n">
         <v>16.05572095033472</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0230089999968186</v>
+        <v>0.02299437497276813</v>
       </c>
       <c r="C2" t="n">
         <v>20.1798782393949</v>
@@ -8845,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02159104199381545</v>
+        <v>0.02190154202980921</v>
       </c>
       <c r="C2" t="n">
         <v>16.18201552721885</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01885304198367521</v>
+        <v>0.01845137501368299</v>
       </c>
       <c r="C2" t="n">
         <v>21.95026985142217</v>
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01796366600319743</v>
+        <v>0.01792554202256724</v>
       </c>
       <c r="C2" t="n">
         <v>22.57096926733922</v>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02655908395536244</v>
+        <v>0.02636395901208743</v>
       </c>
       <c r="C2" t="n">
         <v>26.24079228157473</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01860999997006729</v>
+        <v>0.01874624995980412</v>
       </c>
       <c r="C2" t="n">
         <v>13.9518462508164</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0299744579824619</v>
+        <v>0.02938437496777624</v>
       </c>
       <c r="C2" t="n">
         <v>17.56174429888955</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02433020796161145</v>
+        <v>0.02386029099579901</v>
       </c>
       <c r="C2" t="n">
         <v>15.0082036870514</v>
@@ -9587,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02008324995404109</v>
+        <v>0.01977870799601078</v>
       </c>
       <c r="C2" t="n">
         <v>13.53026701633701</v>
@@ -9693,7 +9693,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02307350002229214</v>
+        <v>0.02298433403484523</v>
       </c>
       <c r="C2" t="n">
         <v>18.29294551819477</v>
@@ -9799,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02132450003409758</v>
+        <v>0.02121825003996491</v>
       </c>
       <c r="C2" t="n">
         <v>23.04578310431127</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02537799999117851</v>
+        <v>0.02296041598310694</v>
       </c>
       <c r="C2" t="n">
         <v>20.73613737729362</v>
@@ -10011,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01896549999946728</v>
+        <v>0.01880470803007483</v>
       </c>
       <c r="C2" t="n">
         <v>15.71535626489778</v>
@@ -10117,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03047162498114631</v>
+        <v>0.02833708300022408</v>
       </c>
       <c r="C2" t="n">
         <v>13.58452293746157</v>
@@ -10223,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02345650002826005</v>
+        <v>0.02262445795349777</v>
       </c>
       <c r="C2" t="n">
         <v>22.02191240296806</v>
@@ -10329,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01961287501035258</v>
+        <v>0.01875716698123142</v>
       </c>
       <c r="C2" t="n">
         <v>18.36045661822892</v>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02511395799228922</v>
+        <v>0.02403804200002924</v>
       </c>
       <c r="C2" t="n">
         <v>14.45958866132876</v>
@@ -10541,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02673641702858731</v>
+        <v>0.02476791699882597</v>
       </c>
       <c r="C2" t="n">
         <v>20.89059430978426</v>
@@ -10647,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0233332909992896</v>
+        <v>0.02274733403464779</v>
       </c>
       <c r="C2" t="n">
         <v>18.95235926736388</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02179629198508337</v>
+        <v>0.02132770797470585</v>
       </c>
       <c r="C2" t="n">
         <v>12.10075358302809</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01770954194944352</v>
+        <v>0.01753654202912003</v>
       </c>
       <c r="C2" t="n">
         <v>25.30118968960324</v>
@@ -10965,7 +10965,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02479883300838992</v>
+        <v>0.02312033297494054</v>
       </c>
       <c r="C2" t="n">
         <v>18.66458328026794</v>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02255512500414625</v>
+        <v>0.02164512500166893</v>
       </c>
       <c r="C2" t="n">
         <v>21.65649280520064</v>
